--- a/resources/templates/standard/F1100-05.xlsx
+++ b/resources/templates/standard/F1100-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>사내교육 관리대장</t>
   </si>
@@ -521,12 +524,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -556,15 +561,15 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
@@ -653,15 +658,15 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -672,7 +677,7 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -686,7 +691,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
@@ -715,7 +720,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -758,7 +763,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -801,7 +806,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
